--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T07:37:23+00:00</t>
+    <t>2024-10-25T08:22:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T08:22:33+00:00</t>
+    <t>2024-10-28T11:11:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T11:11:19+00:00</t>
+    <t>2024-10-28T11:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T11:26:59+00:00</t>
+    <t>2024-10-29T09:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:20:35+00:00</t>
+    <t>2024-10-31T11:17:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T11:17:53+00:00</t>
+    <t>2024-10-31T15:29:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T15:29:56+00:00</t>
+    <t>2024-11-05T14:48:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T14:48:02+00:00</t>
+    <t>2024-11-07T21:06:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:06:19+00:00</t>
+    <t>2024-11-07T21:57:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:57:27+00:00</t>
+    <t>2024-11-07T22:09:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-09T09:07:40+00:00</t>
+    <t>2024-11-11T13:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -704,7 +704,7 @@
     <t>The order of application of coverages is dependent on the types of coverage.</t>
   </si>
   <si>
-    <t>https://www.chipkarte.at/de/vdas-on-fhir/site/ValueSet-ecard-anspruchsarten-vs.html</t>
+    <t>http://svc.co.at/Valueset/ecard-anspruchsarten-vs</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -984,7 +984,7 @@
     <t>Coverage.class:Versichertenarten.type</t>
   </si>
   <si>
-    <t>https://www.chipkarte.at/de/vdas-on-fhir/site/ValueSet-ecard-versichertenarten-vs.html</t>
+    <t>http://svc.co.at/CodeSystem/ecard-versichertenart-vs</t>
   </si>
   <si>
     <t>Coverage.class:Versichertenarten.type.id</t>
@@ -1233,7 +1233,7 @@
     <t>Coverage.class:Versichertenkategorien.type</t>
   </si>
   <si>
-    <t>https://www.chipkarte.at/de/vdas-on-fhir/site/ValueSet-ecard-versichertenkategorien-vs.html</t>
+    <t>http://svc.co.at/CodeSystem/ecard-versichertenkategorie-vs</t>
   </si>
   <si>
     <t>Coverage.class:Versichertenkategorien.type.id</t>
@@ -1878,7 +1878,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="86.8203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="86.33984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:26:20+00:00</t>
+    <t>2024-11-12T06:42:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:42:28+00:00</t>
+    <t>2024-11-12T07:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:20:07+00:00</t>
+    <t>2024-11-12T07:35:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:35:41+00:00</t>
+    <t>2024-11-12T07:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:42:03+00:00</t>
+    <t>2024-11-12T08:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$111</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3622" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4271" uniqueCount="556">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:38:00+00:00</t>
+    <t>2024-11-12T08:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -541,6 +541,10 @@
     <t>Allows coverages to be distinguished and referenced.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -554,6 +558,244 @@
   </si>
   <si>
     <t>C.32, C.33, C.39</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|5.0.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, an absolute URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://tbd-svc/vdasid</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [http://hl7.org/fhir/StructureDefinition/rendered-value](http://hl7.org/fhir/extensions/StructureDefinition-rendered-value.html)). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ident-1
+</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID</t>
+  </si>
+  <si>
+    <t>VDASID</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.id</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.use</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.type</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.system</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.value</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.period</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-organization)
+</t>
   </si>
   <si>
     <t>Coverage.status</t>
@@ -617,36 +859,7 @@
     <t>Coverage.paymentBy.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Coverage.paymentBy.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Coverage.paymentBy.modifierExtension</t>
@@ -691,10 +904,6 @@
     <t>Coverage.type</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Anspruchsart</t>
   </si>
   <si>
@@ -822,9 +1031,6 @@
     <t>The relationship between the patient and the subscriber to determine coordination of benefits.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
   </si>
   <si>
@@ -837,10 +1043,6 @@
     <t>Coverage.period</t>
   </si>
   <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
     <t>Coverage start and end dates</t>
   </si>
   <si>
@@ -863,10 +1065,6 @@
   </si>
   <si>
     <t>Coverage.insurer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
   </si>
   <si>
     <t>Issuer of the policy</t>
@@ -997,9 +1195,6 @@
   </si>
   <si>
     <t>Coverage.class.type.extension</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Coverage.class:Versichertenarten.type.coding</t>
@@ -1850,7 +2045,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP94"/>
+  <dimension ref="A1:AP111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.02734375" customWidth="true" bestFit="true"/>
@@ -1863,7 +2058,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.6328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="86.5390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1872,12 +2067,12 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="86.8203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="56.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
@@ -1890,7 +2085,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="46.53125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="59.44921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="62.85546875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="51.2734375" customWidth="true" bestFit="true"/>
@@ -3417,16 +3612,14 @@
         <v>19</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AC13" s="2"/>
       <c r="AD13" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>160</v>
@@ -3444,19 +3637,19 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>19</v>
@@ -3464,10 +3657,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3475,7 +3668,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>89</v>
@@ -3484,26 +3677,22 @@
         <v>19</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="O14" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>19</v>
       </c>
@@ -3527,52 +3716,52 @@
         <v>19</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AJ14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>19</v>
@@ -3586,21 +3775,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>19</v>
@@ -3609,21 +3798,21 @@
         <v>19</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>19</v>
       </c>
@@ -3647,41 +3836,43 @@
         <v>19</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>19</v>
@@ -3690,7 +3881,7 @@
         <v>19</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>19</v>
@@ -3704,10 +3895,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3718,28 +3909,32 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="O16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>19</v>
       </c>
@@ -3763,13 +3958,13 @@
         <v>19</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>19</v>
+        <v>188</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>19</v>
@@ -3787,13 +3982,13 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>19</v>
@@ -3808,7 +4003,7 @@
         <v>19</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>19</v>
+        <v>191</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>19</v>
@@ -3817,15 +4012,15 @@
         <v>19</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3845,19 +4040,23 @@
         <v>19</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>19</v>
       </c>
@@ -3881,13 +4080,13 @@
         <v>19</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>19</v>
+        <v>199</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>19</v>
@@ -3905,7 +4104,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3914,10 +4113,10 @@
         <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>19</v>
@@ -3926,7 +4125,7 @@
         <v>19</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>19</v>
@@ -3935,26 +4134,26 @@
         <v>19</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>19</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>19</v>
@@ -3963,21 +4162,23 @@
         <v>19</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>19</v>
       </c>
@@ -3986,10 +4187,10 @@
         <v>19</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>19</v>
@@ -4025,19 +4226,19 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>19</v>
@@ -4046,7 +4247,7 @@
         <v>19</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>19</v>
@@ -4055,51 +4256,49 @@
         <v>19</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>19</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>136</v>
+        <v>214</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>19</v>
       </c>
@@ -4111,7 +4310,7 @@
         <v>19</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>19</v>
@@ -4147,19 +4346,19 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>19</v>
+        <v>220</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>19</v>
@@ -4168,7 +4367,7 @@
         <v>19</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>134</v>
+        <v>221</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>19</v>
@@ -4177,15 +4376,15 @@
         <v>19</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>19</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4193,7 +4392,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -4208,13 +4407,13 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4265,10 +4464,10 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>89</v>
@@ -4286,7 +4485,7 @@
         <v>19</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>19</v>
+        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>19</v>
@@ -4295,15 +4494,15 @@
         <v>19</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>19</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4326,15 +4525,17 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>19</v>
@@ -4383,7 +4584,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4404,7 +4605,7 @@
         <v>19</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>19</v>
+        <v>236</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>19</v>
@@ -4413,17 +4614,19 @@
         <v>19</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>19</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>19</v>
       </c>
@@ -4444,17 +4647,19 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>162</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>19</v>
@@ -4479,11 +4684,13 @@
         <v>19</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>218</v>
+        <v>19</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>19</v>
@@ -4501,13 +4708,13 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>160</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>19</v>
@@ -4516,30 +4723,30 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>220</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4559,23 +4766,19 @@
         <v>19</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>207</v>
+        <v>91</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>173</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>19</v>
       </c>
@@ -4623,7 +4826,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4632,47 +4835,47 @@
         <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>226</v>
+        <v>19</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>229</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>19</v>
@@ -4681,23 +4884,21 @@
         <v>19</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>231</v>
+        <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>232</v>
+        <v>179</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>19</v>
       </c>
@@ -4733,57 +4934,57 @@
         <v>19</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>182</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>226</v>
+        <v>19</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>229</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4794,29 +4995,31 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>19</v>
@@ -4841,13 +5044,13 @@
         <v>19</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>19</v>
+        <v>188</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>19</v>
@@ -4865,13 +5068,13 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>190</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>19</v>
@@ -4883,27 +5086,27 @@
         <v>19</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>226</v>
+        <v>19</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>19</v>
+        <v>191</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>229</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4911,7 +5114,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>89</v>
@@ -4926,17 +5129,19 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>243</v>
+        <v>197</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>19</v>
@@ -4961,13 +5166,13 @@
         <v>19</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>19</v>
+        <v>199</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>19</v>
@@ -4985,10 +5190,10 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>89</v>
@@ -5000,30 +5205,30 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>244</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>226</v>
+        <v>19</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>19</v>
+        <v>191</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>229</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5046,19 +5251,19 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>191</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
@@ -5071,7 +5276,7 @@
         <v>19</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>19</v>
@@ -5107,7 +5312,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5128,24 +5333,24 @@
         <v>19</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>251</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>213</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5165,23 +5370,21 @@
         <v>19</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>214</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>253</v>
+        <v>215</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>254</v>
+        <v>216</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>19</v>
       </c>
@@ -5193,7 +5396,7 @@
         <v>19</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>19</v>
@@ -5205,13 +5408,13 @@
         <v>19</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>258</v>
+        <v>19</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>259</v>
+        <v>19</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>19</v>
@@ -5229,7 +5432,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5238,7 +5441,7 @@
         <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>19</v>
+        <v>220</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>101</v>
@@ -5250,24 +5453,24 @@
         <v>19</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>19</v>
+        <v>221</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>260</v>
+        <v>19</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>19</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5290,18 +5493,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>264</v>
+        <v>226</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>265</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>19</v>
       </c>
@@ -5349,7 +5550,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>227</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5364,13 +5565,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>266</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>267</v>
+        <v>19</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>268</v>
+        <v>228</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>19</v>
@@ -5379,15 +5580,15 @@
         <v>19</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>269</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5410,20 +5611,18 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
+        <v>233</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>19</v>
       </c>
@@ -5471,7 +5670,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5492,7 +5691,7 @@
         <v>19</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>19</v>
+        <v>236</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>19</v>
@@ -5501,15 +5700,15 @@
         <v>19</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>19</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5517,34 +5716,34 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -5569,35 +5768,37 @@
         <v>19</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>19</v>
+        <v>255</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>19</v>
@@ -5606,13 +5807,13 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>19</v>
+        <v>256</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>19</v>
+        <v>258</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>19</v>
@@ -5626,10 +5827,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5637,7 +5838,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>89</v>
@@ -5649,19 +5850,21 @@
         <v>19</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>191</v>
+        <v>109</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>19</v>
       </c>
@@ -5685,13 +5888,11 @@
         <v>19</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>19</v>
+        <v>263</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>19</v>
@@ -5709,19 +5910,19 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>19</v>
@@ -5730,7 +5931,7 @@
         <v>19</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>19</v>
@@ -5744,14 +5945,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5770,17 +5971,15 @@
         <v>19</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>136</v>
+        <v>265</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>19</v>
@@ -5829,7 +6028,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5841,7 +6040,7 @@
         <v>19</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>19</v>
@@ -5850,7 +6049,7 @@
         <v>19</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>19</v>
@@ -5864,46 +6063,42 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>136</v>
+        <v>214</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>19</v>
       </c>
@@ -5951,19 +6146,19 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>19</v>
@@ -5972,7 +6167,7 @@
         <v>19</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>19</v>
@@ -5986,21 +6181,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>19</v>
@@ -6009,21 +6204,21 @@
         <v>19</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>179</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>19</v>
       </c>
@@ -6047,13 +6242,13 @@
         <v>19</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>289</v>
+        <v>19</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>290</v>
+        <v>19</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>19</v>
@@ -6071,19 +6266,19 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>285</v>
+        <v>182</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>19</v>
@@ -6092,7 +6287,7 @@
         <v>19</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>19</v>
@@ -6106,45 +6301,45 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>19</v>
+        <v>271</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>294</v>
+        <v>157</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>295</v>
+        <v>158</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6193,19 +6388,19 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>19</v>
@@ -6214,24 +6409,24 @@
         <v>19</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>297</v>
+        <v>19</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>298</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6239,7 +6434,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>89</v>
@@ -6254,18 +6449,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>191</v>
+        <v>276</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>302</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>19</v>
       </c>
@@ -6313,10 +6506,10 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>89</v>
@@ -6337,25 +6530,23 @@
         <v>19</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>297</v>
+        <v>19</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>303</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>19</v>
       </c>
@@ -6367,29 +6558,25 @@
         <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I38" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>19</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>19</v>
       </c>
@@ -6437,13 +6624,13 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>19</v>
@@ -6472,7 +6659,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>282</v>
@@ -6495,19 +6682,21 @@
         <v>19</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>192</v>
+        <v>283</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>193</v>
+        <v>284</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>19</v>
       </c>
@@ -6531,13 +6720,11 @@
         <v>19</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>19</v>
+        <v>286</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>19</v>
@@ -6555,7 +6742,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>194</v>
+        <v>282</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6564,19 +6751,19 @@
         <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>19</v>
+        <v>287</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>19</v>
@@ -6585,26 +6772,26 @@
         <v>19</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>19</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>19</v>
@@ -6613,21 +6800,23 @@
         <v>19</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>136</v>
+        <v>276</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>198</v>
+        <v>290</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>199</v>
+        <v>291</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>19</v>
       </c>
@@ -6675,80 +6864,80 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>200</v>
+        <v>289</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>19</v>
+        <v>294</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>19</v>
+        <v>295</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>19</v>
+        <v>296</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>19</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>136</v>
+        <v>299</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>203</v>
+        <v>300</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>204</v>
+        <v>301</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>157</v>
+        <v>302</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>158</v>
+        <v>303</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>19</v>
@@ -6797,45 +6986,45 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>205</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>19</v>
+        <v>294</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>19</v>
+        <v>295</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>19</v>
+        <v>296</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>19</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6843,10 +7032,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>19</v>
@@ -6858,17 +7047,17 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -6893,11 +7082,13 @@
         <v>19</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>310</v>
+        <v>19</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>19</v>
@@ -6915,13 +7106,13 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>19</v>
@@ -6933,27 +7124,27 @@
         <v>19</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>19</v>
+        <v>294</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>19</v>
+        <v>295</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>19</v>
+        <v>296</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>19</v>
+        <v>297</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6961,7 +7152,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6973,19 +7164,21 @@
         <v>19</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>91</v>
+        <v>299</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>192</v>
+        <v>309</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>193</v>
+        <v>310</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
       </c>
@@ -7033,37 +7226,37 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>194</v>
+        <v>308</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>19</v>
+        <v>312</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>19</v>
+        <v>294</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>19</v>
+        <v>295</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>19</v>
+        <v>296</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>19</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7071,18 +7264,18 @@
         <v>313</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>19</v>
@@ -7091,21 +7284,23 @@
         <v>19</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>136</v>
+        <v>214</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>198</v>
+        <v>314</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>199</v>
+        <v>315</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>19</v>
       </c>
@@ -7141,31 +7336,31 @@
         <v>19</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>315</v>
+        <v>19</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>200</v>
+        <v>313</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>19</v>
@@ -7174,24 +7369,24 @@
         <v>19</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>19</v>
+        <v>318</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>19</v>
+        <v>319</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7202,7 +7397,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>19</v>
@@ -7211,22 +7406,22 @@
         <v>19</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>318</v>
+        <v>193</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7251,13 +7446,13 @@
         <v>19</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>19</v>
+        <v>325</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>19</v>
+        <v>326</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>19</v>
@@ -7275,13 +7470,13 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>19</v>
@@ -7296,24 +7491,24 @@
         <v>19</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>324</v>
+        <v>19</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>19</v>
+        <v>327</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>325</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7333,19 +7528,21 @@
         <v>19</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>192</v>
+        <v>329</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>193</v>
+        <v>330</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>19</v>
       </c>
@@ -7393,7 +7590,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>194</v>
+        <v>328</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7402,19 +7599,19 @@
         <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>19</v>
+        <v>333</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>196</v>
+        <v>334</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>19</v>
@@ -7423,26 +7620,26 @@
         <v>19</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>19</v>
+        <v>335</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>19</v>
@@ -7451,21 +7648,23 @@
         <v>19</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>136</v>
+        <v>231</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>199</v>
+        <v>338</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>19</v>
       </c>
@@ -7501,31 +7700,31 @@
         <v>19</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>315</v>
+        <v>19</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>200</v>
+        <v>336</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>19</v>
@@ -7534,7 +7733,7 @@
         <v>19</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>19</v>
@@ -7548,10 +7747,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7562,7 +7761,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>19</v>
@@ -7571,22 +7770,22 @@
         <v>19</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>103</v>
+        <v>265</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -7596,7 +7795,7 @@
         <v>19</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>336</v>
+        <v>19</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>19</v>
@@ -7623,25 +7822,23 @@
         <v>19</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>19</v>
@@ -7656,7 +7853,7 @@
         <v>19</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>338</v>
+        <v>19</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>19</v>
@@ -7665,15 +7862,15 @@
         <v>19</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>339</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7693,20 +7890,18 @@
         <v>19</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>342</v>
+        <v>173</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7755,7 +7950,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>345</v>
+        <v>175</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7764,10 +7959,10 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>19</v>
@@ -7776,7 +7971,7 @@
         <v>19</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>346</v>
+        <v>177</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>19</v>
@@ -7785,7 +7980,7 @@
         <v>19</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>347</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7793,18 +7988,18 @@
         <v>348</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>19</v>
@@ -7813,21 +8008,21 @@
         <v>19</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>350</v>
+        <v>179</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>19</v>
       </c>
@@ -7875,19 +8070,19 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>353</v>
+        <v>182</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>19</v>
@@ -7896,7 +8091,7 @@
         <v>19</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>355</v>
+        <v>177</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>19</v>
@@ -7905,48 +8100,50 @@
         <v>19</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>356</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>19</v>
+        <v>271</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>136</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>359</v>
+        <v>272</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>361</v>
+        <v>158</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -7995,19 +8192,19 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>362</v>
+        <v>274</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
@@ -8016,7 +8213,7 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>363</v>
+        <v>134</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>19</v>
@@ -8025,15 +8222,15 @@
         <v>19</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>364</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8041,7 +8238,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
@@ -8056,19 +8253,17 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>367</v>
+        <v>193</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -8093,13 +8288,13 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>19</v>
+        <v>354</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>19</v>
+        <v>355</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -8117,10 +8312,10 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>89</v>
@@ -8138,7 +8333,7 @@
         <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>373</v>
+        <v>19</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>19</v>
@@ -8147,15 +8342,15 @@
         <v>19</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>374</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8163,7 +8358,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>89</v>
@@ -8178,19 +8373,19 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>19</v>
@@ -8239,10 +8434,10 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>89</v>
@@ -8260,24 +8455,24 @@
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>382</v>
+        <v>19</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>383</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>291</v>
+        <v>364</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8285,7 +8480,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>89</v>
@@ -8300,19 +8495,17 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>161</v>
+        <v>214</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>292</v>
+        <v>365</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>295</v>
+        <v>367</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -8361,10 +8554,10 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>291</v>
+        <v>364</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>89</v>
@@ -8385,23 +8578,25 @@
         <v>19</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>296</v>
+        <v>361</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>297</v>
+        <v>362</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>298</v>
+        <v>368</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>19</v>
       </c>
@@ -8413,26 +8608,28 @@
         <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>191</v>
+        <v>265</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>302</v>
+        <v>345</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>19</v>
@@ -8481,13 +8678,13 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>19</v>
@@ -8505,25 +8702,23 @@
         <v>19</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>297</v>
+        <v>19</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>303</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>19</v>
       </c>
@@ -8535,7 +8730,7 @@
         <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>19</v>
@@ -8544,20 +8739,16 @@
         <v>19</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>387</v>
+        <v>173</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>19</v>
       </c>
@@ -8605,19 +8796,19 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>19</v>
@@ -8626,7 +8817,7 @@
         <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>19</v>
@@ -8640,21 +8831,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>282</v>
+        <v>348</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>19</v>
@@ -8666,15 +8857,17 @@
         <v>19</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>191</v>
+        <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>19</v>
@@ -8723,19 +8916,19 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>19</v>
@@ -8744,7 +8937,7 @@
         <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>19</v>
@@ -8758,14 +8951,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>283</v>
+        <v>349</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>154</v>
+        <v>271</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8778,24 +8971,26 @@
         <v>19</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>198</v>
+        <v>272</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>199</v>
+        <v>273</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>19</v>
       </c>
@@ -8843,7 +9038,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>200</v>
+        <v>274</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8864,7 +9059,7 @@
         <v>19</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>19</v>
@@ -8878,45 +9073,43 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>203</v>
+        <v>351</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>158</v>
+        <v>353</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -8941,13 +9134,11 @@
         <v>19</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>19</v>
+        <v>375</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>19</v>
@@ -8965,19 +9156,19 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>205</v>
+        <v>350</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>19</v>
@@ -8986,7 +9177,7 @@
         <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>19</v>
@@ -9000,10 +9191,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>285</v>
+        <v>377</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9011,7 +9202,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>89</v>
@@ -9023,21 +9214,19 @@
         <v>19</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>214</v>
+        <v>91</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>286</v>
+        <v>173</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>287</v>
+        <v>174</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>288</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>19</v>
       </c>
@@ -9061,11 +9250,13 @@
         <v>19</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>392</v>
+        <v>19</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>19</v>
@@ -9083,19 +9274,19 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>285</v>
+        <v>175</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>19</v>
@@ -9104,7 +9295,7 @@
         <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>19</v>
@@ -9118,21 +9309,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>312</v>
+        <v>379</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>19</v>
@@ -9144,15 +9335,17 @@
         <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>19</v>
@@ -9189,31 +9382,31 @@
         <v>19</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>19</v>
@@ -9222,7 +9415,7 @@
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>19</v>
@@ -9236,14 +9429,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>314</v>
+        <v>381</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9259,21 +9452,23 @@
         <v>19</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>136</v>
+        <v>382</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>198</v>
+        <v>383</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>199</v>
+        <v>384</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>19</v>
       </c>
@@ -9309,19 +9504,19 @@
         <v>19</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>315</v>
+        <v>19</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>200</v>
+        <v>387</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9333,7 +9528,7 @@
         <v>19</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>19</v>
@@ -9342,7 +9537,7 @@
         <v>19</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>196</v>
+        <v>388</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>19</v>
@@ -9351,15 +9546,15 @@
         <v>19</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>19</v>
+        <v>389</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>317</v>
+        <v>391</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9370,7 +9565,7 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>19</v>
@@ -9379,23 +9574,19 @@
         <v>19</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>318</v>
+        <v>91</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>319</v>
+        <v>173</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>19</v>
       </c>
@@ -9443,19 +9634,19 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>323</v>
+        <v>175</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>19</v>
@@ -9464,7 +9655,7 @@
         <v>19</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>19</v>
@@ -9473,26 +9664,26 @@
         <v>19</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>325</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>19</v>
@@ -9504,15 +9695,17 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>19</v>
@@ -9549,31 +9742,31 @@
         <v>19</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>19</v>
@@ -9582,7 +9775,7 @@
         <v>19</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>19</v>
@@ -9596,21 +9789,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>19</v>
@@ -9619,21 +9812,23 @@
         <v>19</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>198</v>
+        <v>396</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>199</v>
+        <v>397</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
       </c>
@@ -9642,7 +9837,7 @@
         <v>19</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>19</v>
+        <v>400</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>19</v>
@@ -9669,31 +9864,31 @@
         <v>19</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>315</v>
+        <v>19</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>200</v>
+        <v>401</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>19</v>
@@ -9702,7 +9897,7 @@
         <v>19</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>196</v>
+        <v>402</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>19</v>
@@ -9711,15 +9906,15 @@
         <v>19</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>19</v>
+        <v>403</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>331</v>
+        <v>405</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9742,20 +9937,18 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>103</v>
+        <v>214</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>332</v>
+        <v>406</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>333</v>
+        <v>407</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>19</v>
       </c>
@@ -9764,7 +9957,7 @@
         <v>19</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>399</v>
+        <v>19</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>19</v>
@@ -9803,7 +9996,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>337</v>
+        <v>409</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9824,7 +10017,7 @@
         <v>19</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>338</v>
+        <v>410</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>19</v>
@@ -9833,15 +10026,15 @@
         <v>19</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>339</v>
+        <v>411</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>341</v>
+        <v>413</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9864,18 +10057,18 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>191</v>
+        <v>109</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>342</v>
+        <v>414</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>19</v>
       </c>
@@ -9923,7 +10116,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>345</v>
+        <v>417</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9932,7 +10125,7 @@
         <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>19</v>
+        <v>418</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>101</v>
@@ -9944,7 +10137,7 @@
         <v>19</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>346</v>
+        <v>419</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>19</v>
@@ -9953,15 +10146,15 @@
         <v>19</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>347</v>
+        <v>420</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>349</v>
+        <v>422</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9984,17 +10177,17 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>109</v>
+        <v>214</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>350</v>
+        <v>423</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>351</v>
+        <v>424</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>352</v>
+        <v>425</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -10043,7 +10236,7 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>353</v>
+        <v>426</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10052,7 +10245,7 @@
         <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>354</v>
+        <v>418</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>101</v>
@@ -10064,7 +10257,7 @@
         <v>19</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>355</v>
+        <v>427</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>19</v>
@@ -10073,15 +10266,15 @@
         <v>19</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>356</v>
+        <v>428</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>358</v>
+        <v>430</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10104,17 +10297,19 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>191</v>
+        <v>431</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>359</v>
+        <v>432</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="O69" t="s" s="2">
-        <v>361</v>
+        <v>435</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>19</v>
@@ -10163,7 +10358,7 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>362</v>
+        <v>436</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10172,7 +10367,7 @@
         <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>101</v>
@@ -10184,7 +10379,7 @@
         <v>19</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>363</v>
+        <v>437</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>19</v>
@@ -10193,15 +10388,15 @@
         <v>19</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>364</v>
+        <v>438</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>403</v>
+        <v>439</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>366</v>
+        <v>440</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10224,19 +10419,19 @@
         <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>367</v>
+        <v>214</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>368</v>
+        <v>441</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>369</v>
+        <v>442</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>370</v>
+        <v>443</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>371</v>
+        <v>444</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>19</v>
@@ -10285,7 +10480,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>372</v>
+        <v>445</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10306,7 +10501,7 @@
         <v>19</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>373</v>
+        <v>446</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>19</v>
@@ -10315,15 +10510,15 @@
         <v>19</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>374</v>
+        <v>447</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>404</v>
+        <v>448</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10331,7 +10526,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>89</v>
@@ -10346,19 +10541,19 @@
         <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -10407,10 +10602,10 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>89</v>
@@ -10428,24 +10623,24 @@
         <v>19</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>382</v>
+        <v>19</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>383</v>
+        <v>363</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>291</v>
+        <v>364</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10453,7 +10648,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>89</v>
@@ -10468,19 +10663,17 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>161</v>
+        <v>214</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>292</v>
+        <v>365</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>295</v>
+        <v>367</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -10529,10 +10722,10 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>291</v>
+        <v>364</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>89</v>
@@ -10553,23 +10746,25 @@
         <v>19</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>296</v>
+        <v>361</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>297</v>
+        <v>362</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>298</v>
+        <v>368</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>19</v>
       </c>
@@ -10581,26 +10776,28 @@
         <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>191</v>
+        <v>265</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>300</v>
+        <v>451</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O73" t="s" s="2">
-        <v>302</v>
+        <v>345</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>19</v>
@@ -10649,13 +10846,13 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>19</v>
@@ -10673,21 +10870,21 @@
         <v>19</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>297</v>
+        <v>19</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>303</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>407</v>
+        <v>452</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>407</v>
+        <v>347</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10707,21 +10904,19 @@
         <v>19</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>408</v>
+        <v>214</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>409</v>
+        <v>173</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>410</v>
+        <v>174</v>
       </c>
       <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>411</v>
-      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>19</v>
       </c>
@@ -10769,7 +10964,7 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>407</v>
+        <v>175</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10778,10 +10973,10 @@
         <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>19</v>
@@ -10790,7 +10985,7 @@
         <v>19</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>19</v>
@@ -10804,21 +10999,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>412</v>
+        <v>453</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>412</v>
+        <v>348</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>19</v>
@@ -10827,21 +11022,21 @@
         <v>19</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>191</v>
+        <v>136</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>413</v>
+        <v>179</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>19</v>
       </c>
@@ -10889,19 +11084,19 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>412</v>
+        <v>182</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>19</v>
@@ -10910,10 +11105,10 @@
         <v>19</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>416</v>
+        <v>19</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>19</v>
@@ -10924,14 +11119,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>417</v>
+        <v>454</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>417</v>
+        <v>349</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>418</v>
+        <v>271</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10944,25 +11139,25 @@
         <v>19</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>419</v>
+        <v>272</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>420</v>
+        <v>273</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>421</v>
+        <v>157</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>422</v>
+        <v>158</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>19</v>
@@ -11011,7 +11206,7 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>417</v>
+        <v>274</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11023,7 +11218,7 @@
         <v>19</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>19</v>
@@ -11032,7 +11227,7 @@
         <v>19</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>19</v>
@@ -11046,10 +11241,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>423</v>
+        <v>455</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>423</v>
+        <v>350</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11057,7 +11252,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>89</v>
@@ -11069,19 +11264,21 @@
         <v>19</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>192</v>
+        <v>351</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>193</v>
+        <v>352</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>19</v>
       </c>
@@ -11105,13 +11302,11 @@
         <v>19</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>19</v>
+        <v>456</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>19</v>
@@ -11129,19 +11324,19 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>194</v>
+        <v>350</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>19</v>
@@ -11150,7 +11345,7 @@
         <v>19</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>19</v>
@@ -11164,21 +11359,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>424</v>
+        <v>457</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>424</v>
+        <v>377</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>19</v>
@@ -11190,17 +11385,15 @@
         <v>19</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>19</v>
@@ -11249,19 +11442,19 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>19</v>
@@ -11270,7 +11463,7 @@
         <v>19</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>19</v>
@@ -11284,14 +11477,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>425</v>
+        <v>458</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>425</v>
+        <v>379</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11304,26 +11497,24 @@
         <v>19</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O79" t="s" s="2">
-        <v>158</v>
-      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>19</v>
       </c>
@@ -11359,19 +11550,19 @@
         <v>19</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11392,7 +11583,7 @@
         <v>19</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>19</v>
@@ -11406,10 +11597,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>426</v>
+        <v>459</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>426</v>
+        <v>381</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11420,7 +11611,7 @@
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>19</v>
@@ -11432,19 +11623,19 @@
         <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>214</v>
+        <v>382</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>427</v>
+        <v>383</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>428</v>
+        <v>384</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>429</v>
+        <v>385</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>430</v>
+        <v>386</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>19</v>
@@ -11469,13 +11660,13 @@
         <v>19</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>431</v>
+        <v>19</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>432</v>
+        <v>19</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>19</v>
@@ -11493,13 +11684,13 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>426</v>
+        <v>387</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>19</v>
@@ -11514,7 +11705,7 @@
         <v>19</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>19</v>
+        <v>388</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>19</v>
@@ -11523,15 +11714,15 @@
         <v>19</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>19</v>
+        <v>389</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>433</v>
+        <v>460</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>433</v>
+        <v>391</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11554,20 +11745,16 @@
         <v>19</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>214</v>
+        <v>91</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>434</v>
+        <v>173</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>19</v>
       </c>
@@ -11591,11 +11778,13 @@
         <v>19</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="Y81" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z81" t="s" s="2">
-        <v>439</v>
+        <v>19</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>19</v>
@@ -11613,7 +11802,7 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>433</v>
+        <v>175</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11622,10 +11811,10 @@
         <v>89</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>19</v>
@@ -11634,7 +11823,7 @@
         <v>19</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>19</v>
@@ -11648,21 +11837,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>440</v>
+        <v>393</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>19</v>
@@ -11674,18 +11863,18 @@
         <v>19</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>441</v>
+        <v>179</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>19</v>
       </c>
@@ -11709,41 +11898,43 @@
         <v>19</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>444</v>
+        <v>19</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>440</v>
+        <v>182</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>19</v>
@@ -11752,7 +11943,7 @@
         <v>19</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>19</v>
@@ -11766,10 +11957,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>445</v>
+        <v>395</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11789,20 +11980,22 @@
         <v>19</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>214</v>
+        <v>103</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>446</v>
+        <v>396</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O83" t="s" s="2">
-        <v>448</v>
+        <v>399</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>19</v>
@@ -11812,7 +12005,7 @@
         <v>19</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>19</v>
+        <v>463</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>19</v>
@@ -11827,11 +12020,13 @@
         <v>19</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>449</v>
+        <v>19</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>19</v>
@@ -11849,7 +12044,7 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>445</v>
+        <v>401</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11870,7 +12065,7 @@
         <v>19</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>19</v>
+        <v>402</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>19</v>
@@ -11879,15 +12074,15 @@
         <v>19</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>19</v>
+        <v>403</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>450</v>
+        <v>405</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11907,21 +12102,21 @@
         <v>19</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>214</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>451</v>
+        <v>406</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>19</v>
       </c>
@@ -11945,11 +12140,13 @@
         <v>19</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>453</v>
+        <v>19</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>19</v>
@@ -11967,7 +12164,7 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>450</v>
+        <v>409</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11988,7 +12185,7 @@
         <v>19</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>19</v>
+        <v>410</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>19</v>
@@ -11997,15 +12194,15 @@
         <v>19</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>19</v>
+        <v>411</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>454</v>
+        <v>413</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12028,19 +12225,17 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>455</v>
+        <v>109</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>456</v>
+        <v>414</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>459</v>
+        <v>416</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>19</v>
@@ -12089,7 +12284,7 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>454</v>
+        <v>417</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12098,7 +12293,7 @@
         <v>89</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>19</v>
+        <v>418</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>101</v>
@@ -12110,24 +12305,24 @@
         <v>19</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>19</v>
+        <v>419</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>297</v>
+        <v>19</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>303</v>
+        <v>420</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>460</v>
+        <v>422</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12138,7 +12333,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>19</v>
@@ -12147,20 +12342,20 @@
         <v>19</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>461</v>
+        <v>423</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>462</v>
+        <v>424</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>19</v>
@@ -12209,16 +12404,16 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>460</v>
+        <v>426</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>19</v>
+        <v>418</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>101</v>
@@ -12230,7 +12425,7 @@
         <v>19</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>19</v>
@@ -12239,15 +12434,15 @@
         <v>19</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>19</v>
+        <v>428</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>463</v>
+        <v>430</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12267,19 +12462,23 @@
         <v>19</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>191</v>
+        <v>431</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>192</v>
+        <v>432</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>19</v>
       </c>
@@ -12327,7 +12526,7 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>194</v>
+        <v>436</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12336,10 +12535,10 @@
         <v>89</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>19</v>
@@ -12348,7 +12547,7 @@
         <v>19</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>196</v>
+        <v>437</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>19</v>
@@ -12357,26 +12556,26 @@
         <v>19</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>19</v>
+        <v>438</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>19</v>
@@ -12385,21 +12584,23 @@
         <v>19</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>136</v>
+        <v>214</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>198</v>
+        <v>441</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>199</v>
+        <v>442</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>19</v>
       </c>
@@ -12447,19 +12648,19 @@
         <v>19</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>200</v>
+        <v>445</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>19</v>
@@ -12468,7 +12669,7 @@
         <v>19</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>196</v>
+        <v>446</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>19</v>
@@ -12477,50 +12678,50 @@
         <v>19</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>19</v>
+        <v>447</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>465</v>
+        <v>356</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>203</v>
+        <v>357</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>204</v>
+        <v>358</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>157</v>
+        <v>359</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>158</v>
+        <v>360</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>19</v>
@@ -12569,19 +12770,19 @@
         <v>19</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>205</v>
+        <v>356</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>19</v>
@@ -12590,24 +12791,24 @@
         <v>19</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>19</v>
+        <v>363</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>466</v>
+        <v>364</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12615,7 +12816,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>89</v>
@@ -12633,14 +12834,14 @@
         <v>214</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>467</v>
+        <v>365</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>468</v>
+        <v>366</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>469</v>
+        <v>367</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>19</v>
@@ -12665,13 +12866,13 @@
         <v>19</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>438</v>
+        <v>19</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>470</v>
+        <v>19</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>471</v>
+        <v>19</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>19</v>
@@ -12689,10 +12890,10 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>466</v>
+        <v>364</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>89</v>
@@ -12713,21 +12914,21 @@
         <v>19</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>19</v>
+        <v>368</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12750,7 +12951,7 @@
         <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>262</v>
+        <v>472</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>473</v>
@@ -12809,7 +13010,7 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12867,10 +13068,10 @@
         <v>19</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>367</v>
+        <v>214</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>477</v>
@@ -12878,11 +13079,9 @@
       <c r="M92" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="N92" s="2"/>
+      <c r="O92" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>19</v>
@@ -12955,7 +13154,7 @@
         <v>19</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>19</v>
+        <v>480</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>19</v>
@@ -12973,7 +13172,7 @@
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>19</v>
+        <v>482</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12992,7 +13191,7 @@
         <v>19</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>482</v>
+        <v>265</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>483</v>
@@ -13000,9 +13199,11 @@
       <c r="M93" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N93" s="2"/>
+      <c r="N93" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="O93" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>19</v>
@@ -13072,16 +13273,16 @@
         <v>19</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>486</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" hidden="true">
@@ -13112,18 +13313,16 @@
         <v>19</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>488</v>
+        <v>214</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>489</v>
+        <v>173</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>490</v>
+        <v>174</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" t="s" s="2">
-        <v>491</v>
-      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>19</v>
       </c>
@@ -13171,7 +13370,7 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>487</v>
+        <v>175</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13180,32 +13379,2074 @@
         <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="AJ94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK94" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP94" t="s" s="2">
+      <c r="AK97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="Y98" s="2"/>
+      <c r="Z98" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="Y99" s="2"/>
+      <c r="Z99" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="Y100" s="2"/>
+      <c r="Z100" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="Y101" s="2"/>
+      <c r="Z101" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP111" t="s" s="2">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP94">
+  <autoFilter ref="A1:AP111">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13215,7 +15456,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI93">
+  <conditionalFormatting sqref="A2:AI110">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$103</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4271" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3966" uniqueCount="556">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:47:06+00:00</t>
+    <t>2024-11-12T20:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -560,6 +560,15 @@
     <t>C.32, C.33, C.39</t>
   </si>
   <si>
+    <t>Coverage.identifier:VDASID</t>
+  </si>
+  <si>
+    <t>VDASID</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.id</t>
+  </si>
+  <si>
     <t>Coverage.identifier.id</t>
   </si>
   <si>
@@ -579,6 +588,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>Coverage.identifier:VDASID.extension</t>
+  </si>
+  <si>
     <t>Coverage.identifier.extension</t>
   </si>
   <si>
@@ -594,6 +606,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>Coverage.identifier:VDASID.use</t>
+  </si>
+  <si>
     <t>Coverage.identifier.use</t>
   </si>
   <si>
@@ -619,6 +634,9 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.type</t>
   </si>
   <si>
     <t>Coverage.identifier.type</t>
@@ -655,6 +673,9 @@
     <t>CX.5</t>
   </si>
   <si>
+    <t>Coverage.identifier:VDASID.system</t>
+  </si>
+  <si>
     <t>Coverage.identifier.system</t>
   </si>
   <si>
@@ -683,6 +704,9 @@
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.value</t>
   </si>
   <si>
     <t>Coverage.identifier.value</t>
@@ -717,6 +741,9 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
+    <t>Coverage.identifier:VDASID.period</t>
+  </si>
+  <si>
     <t>Coverage.identifier.period</t>
   </si>
   <si>
@@ -739,332 +766,305 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
+    <t>Coverage.identifier:VDASID.assigner</t>
+  </si>
+  <si>
     <t>Coverage.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>Coverage.status</t>
+  </si>
+  <si>
+    <t>active | cancelled | draft | entered-in-error</t>
+  </si>
+  <si>
+    <t>The status of the resource instance.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the status contains the code entered-in-error that marks the coverage as not currently valid.</t>
+  </si>
+  <si>
+    <t>Need to track the status of the resource as 'draft' resources may undergo further edits while 'active' resources are immutable and may only have their status changed to 'cancelled'.</t>
+  </si>
+  <si>
+    <t>A code specifying the state of the resource instance.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/fm-status|5.0.0</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Act.status</t>
+  </si>
+  <si>
+    <t>Coverage.kind</t>
+  </si>
+  <si>
+    <t>insurance | self-pay | other</t>
+  </si>
+  <si>
+    <t>The nature of the coverage be it insurance, or cash payment such as self-pay.</t>
+  </si>
+  <si>
+    <t>This is used to implement conformance on other elements.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/coverage-kind|5.0.0</t>
+  </si>
+  <si>
+    <t>Coverage.paymentBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Self-pay parties and responsibility</t>
+  </si>
+  <si>
+    <t>Link to the paying party and optionally what specifically they will be responsible to pay.</t>
+  </si>
+  <si>
+    <t>Coverage.paymentBy.id</t>
+  </si>
+  <si>
+    <t>Coverage.paymentBy.extension</t>
+  </si>
+  <si>
+    <t>Coverage.paymentBy.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Coverage.paymentBy.party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|RelatedPerson|Organization)
+</t>
+  </si>
+  <si>
+    <t>Parties performing self-payment</t>
+  </si>
+  <si>
+    <t>The list of parties providing non-insurance payment for the treatment costs.</t>
+  </si>
+  <si>
+    <t>Coverage.paymentBy.responsibility</t>
+  </si>
+  <si>
+    <t>Party's responsibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Description of the financial responsibility.</t>
+  </si>
+  <si>
+    <t>Coverage.type</t>
+  </si>
+  <si>
+    <t>Anspruchsart</t>
+  </si>
+  <si>
+    <t>The type of coverage: social program, medical plan, accident coverage (workers compensation, auto), group health or payment by an individual or organization.</t>
+  </si>
+  <si>
+    <t>The order of application of coverages is dependent on the types of coverage.</t>
+  </si>
+  <si>
+    <t>http://svc.co.at/Valueset/ecard-anspruchsarten-vs</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>IN1-15</t>
+  </si>
+  <si>
+    <t>Coverage.policyHolder</t>
+  </si>
+  <si>
+    <t>Owner of the policy</t>
+  </si>
+  <si>
+    <t>The party who 'owns' the insurance policy.</t>
+  </si>
+  <si>
+    <t>For example: may be an individual, corporation or the subscriber's employer.</t>
+  </si>
+  <si>
+    <t>This provides employer information in the case of Worker's Compensation and other policies.</t>
+  </si>
+  <si>
+    <t>FiveWs.subject[x]</t>
+  </si>
+  <si>
+    <t>D01 through D09</t>
+  </si>
+  <si>
+    <t>C.35</t>
+  </si>
+  <si>
+    <t>IN1-16, 18,  19-name of insured, address, date of birth</t>
+  </si>
+  <si>
+    <t>Coverage.subscriber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-patient)
+</t>
+  </si>
+  <si>
+    <t>Subscriber to the policy</t>
+  </si>
+  <si>
+    <t>The party who has signed-up for or 'owns' the contractual relationship to the policy or to whom the benefit of the policy for services rendered to them or their family is due.</t>
+  </si>
+  <si>
+    <t>May be self or a parent in the case of dependants. A subscriber is only required on certain types of policies not all policies and that it is appropriate to have just a policyholder and a beneficiary when not other party can join that policy instance.</t>
+  </si>
+  <si>
+    <t>This is the party who is entitled to the benfits under the policy.</t>
+  </si>
+  <si>
+    <t>Coverage.subscriberId</t>
+  </si>
+  <si>
+    <t>ID assigned to the subscriber</t>
+  </si>
+  <si>
+    <t>The insurer assigned ID for the Subscriber.</t>
+  </si>
+  <si>
+    <t>The insurer requires this identifier on correspondance and claims (digital and otherwise).</t>
+  </si>
+  <si>
+    <t>Coverage.beneficiary</t>
+  </si>
+  <si>
+    <t>Plan beneficiary</t>
+  </si>
+  <si>
+    <t>The party who benefits from the insurance coverage; the patient when products and/or services are provided.</t>
+  </si>
+  <si>
+    <t>This is the party who receives treatment for which the costs are reimbursed under the coverage.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>Coverage.dependent</t>
+  </si>
+  <si>
+    <t>Dependent number</t>
+  </si>
+  <si>
+    <t>A designator for a dependent under the coverage.</t>
+  </si>
+  <si>
+    <t>Sometimes the member number is constructed from the subscriberId and the dependant number.</t>
+  </si>
+  <si>
+    <t>For some coverages a single identifier is issued to the Subscriber and then an additional dependent number is issued to each beneficiary.</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>- No exact HL7 V2 equivalent concept seems to exist;</t>
+  </si>
+  <si>
+    <t>Coverage.relationship</t>
+  </si>
+  <si>
+    <t>Beneficiary relationship to the subscriber</t>
+  </si>
+  <si>
+    <t>The relationship of beneficiary (patient) to the subscriber.</t>
+  </si>
+  <si>
+    <t>Typically, an individual uses policies which are theirs (relationship='self') before policies owned by others.</t>
+  </si>
+  <si>
+    <t>The relationship between the patient and the subscriber to determine coordination of benefits.</t>
+  </si>
+  <si>
+    <t>The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship</t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>Coverage.period</t>
+  </si>
+  <si>
+    <t>Coverage start and end dates</t>
+  </si>
+  <si>
+    <t>Time period during which the coverage is in force. A missing start date indicates the start date isn't known, a missing end date means the coverage is continuing to be in force.</t>
+  </si>
+  <si>
+    <t>Some insurers require the submission of the coverage term.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Act.effectiveTime</t>
+  </si>
+  <si>
+    <t>IN1-12 / IN1-13</t>
+  </si>
+  <si>
+    <t>Coverage.insurer</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Organization)
 </t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID</t>
-  </si>
-  <si>
-    <t>VDASID</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.id</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.extension</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.use</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.type</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.system</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.value</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.period</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-organization)
-</t>
-  </si>
-  <si>
-    <t>Coverage.status</t>
-  </si>
-  <si>
-    <t>active | cancelled | draft | entered-in-error</t>
-  </si>
-  <si>
-    <t>The status of the resource instance.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains the code entered-in-error that marks the coverage as not currently valid.</t>
-  </si>
-  <si>
-    <t>Need to track the status of the resource as 'draft' resources may undergo further edits while 'active' resources are immutable and may only have their status changed to 'cancelled'.</t>
-  </si>
-  <si>
-    <t>A code specifying the state of the resource instance.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/fm-status|5.0.0</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Act.status</t>
-  </si>
-  <si>
-    <t>Coverage.kind</t>
-  </si>
-  <si>
-    <t>insurance | self-pay | other</t>
-  </si>
-  <si>
-    <t>The nature of the coverage be it insurance, or cash payment such as self-pay.</t>
-  </si>
-  <si>
-    <t>This is used to implement conformance on other elements.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-kind|5.0.0</t>
-  </si>
-  <si>
-    <t>Coverage.paymentBy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Self-pay parties and responsibility</t>
-  </si>
-  <si>
-    <t>Link to the paying party and optionally what specifically they will be responsible to pay.</t>
-  </si>
-  <si>
-    <t>Coverage.paymentBy.id</t>
-  </si>
-  <si>
-    <t>Coverage.paymentBy.extension</t>
-  </si>
-  <si>
-    <t>Coverage.paymentBy.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Coverage.paymentBy.party</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Organization)
-</t>
-  </si>
-  <si>
-    <t>Parties performing self-payment</t>
-  </si>
-  <si>
-    <t>The list of parties providing non-insurance payment for the treatment costs.</t>
-  </si>
-  <si>
-    <t>Coverage.paymentBy.responsibility</t>
-  </si>
-  <si>
-    <t>Party's responsibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Description of the financial responsibility.</t>
-  </si>
-  <si>
-    <t>Coverage.type</t>
-  </si>
-  <si>
-    <t>Anspruchsart</t>
-  </si>
-  <si>
-    <t>The type of coverage: social program, medical plan, accident coverage (workers compensation, auto), group health or payment by an individual or organization.</t>
-  </si>
-  <si>
-    <t>The order of application of coverages is dependent on the types of coverage.</t>
-  </si>
-  <si>
-    <t>http://svc.co.at/Valueset/ecard-anspruchsarten-vs</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>IN1-15</t>
-  </si>
-  <si>
-    <t>Coverage.policyHolder</t>
-  </si>
-  <si>
-    <t>Owner of the policy</t>
-  </si>
-  <si>
-    <t>The party who 'owns' the insurance policy.</t>
-  </si>
-  <si>
-    <t>For example: may be an individual, corporation or the subscriber's employer.</t>
-  </si>
-  <si>
-    <t>This provides employer information in the case of Worker's Compensation and other policies.</t>
-  </si>
-  <si>
-    <t>FiveWs.subject[x]</t>
-  </si>
-  <si>
-    <t>D01 through D09</t>
-  </si>
-  <si>
-    <t>C.35</t>
-  </si>
-  <si>
-    <t>IN1-16, 18,  19-name of insured, address, date of birth</t>
-  </si>
-  <si>
-    <t>Coverage.subscriber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-patient)
-</t>
-  </si>
-  <si>
-    <t>Subscriber to the policy</t>
-  </si>
-  <si>
-    <t>The party who has signed-up for or 'owns' the contractual relationship to the policy or to whom the benefit of the policy for services rendered to them or their family is due.</t>
-  </si>
-  <si>
-    <t>May be self or a parent in the case of dependants. A subscriber is only required on certain types of policies not all policies and that it is appropriate to have just a policyholder and a beneficiary when not other party can join that policy instance.</t>
-  </si>
-  <si>
-    <t>This is the party who is entitled to the benfits under the policy.</t>
-  </si>
-  <si>
-    <t>Coverage.subscriberId</t>
-  </si>
-  <si>
-    <t>ID assigned to the subscriber</t>
-  </si>
-  <si>
-    <t>The insurer assigned ID for the Subscriber.</t>
-  </si>
-  <si>
-    <t>The insurer requires this identifier on correspondance and claims (digital and otherwise).</t>
-  </si>
-  <si>
-    <t>Coverage.beneficiary</t>
-  </si>
-  <si>
-    <t>Plan beneficiary</t>
-  </si>
-  <si>
-    <t>The party who benefits from the insurance coverage; the patient when products and/or services are provided.</t>
-  </si>
-  <si>
-    <t>This is the party who receives treatment for which the costs are reimbursed under the coverage.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>Coverage.dependent</t>
-  </si>
-  <si>
-    <t>Dependent number</t>
-  </si>
-  <si>
-    <t>A designator for a dependent under the coverage.</t>
-  </si>
-  <si>
-    <t>Sometimes the member number is constructed from the subscriberId and the dependant number.</t>
-  </si>
-  <si>
-    <t>For some coverages a single identifier is issued to the Subscriber and then an additional dependent number is issued to each beneficiary.</t>
-  </si>
-  <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t>- No exact HL7 V2 equivalent concept seems to exist;</t>
-  </si>
-  <si>
-    <t>Coverage.relationship</t>
-  </si>
-  <si>
-    <t>Beneficiary relationship to the subscriber</t>
-  </si>
-  <si>
-    <t>The relationship of beneficiary (patient) to the subscriber.</t>
-  </si>
-  <si>
-    <t>Typically, an individual uses policies which are theirs (relationship='self') before policies owned by others.</t>
-  </si>
-  <si>
-    <t>The relationship between the patient and the subscriber to determine coordination of benefits.</t>
-  </si>
-  <si>
-    <t>The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship</t>
-  </si>
-  <si>
-    <t>C03</t>
-  </si>
-  <si>
-    <t>Coverage.period</t>
-  </si>
-  <si>
-    <t>Coverage start and end dates</t>
-  </si>
-  <si>
-    <t>Time period during which the coverage is in force. A missing start date indicates the start date isn't known, a missing end date means the coverage is continuing to be in force.</t>
-  </si>
-  <si>
-    <t>Some insurers require the submission of the coverage term.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Act.effectiveTime</t>
-  </si>
-  <si>
-    <t>IN1-12 / IN1-13</t>
-  </si>
-  <si>
-    <t>Coverage.insurer</t>
   </si>
   <si>
     <t>Issuer of the policy</t>
@@ -2045,7 +2045,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP111"/>
+  <dimension ref="A1:AP103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.02734375" customWidth="true" bestFit="true"/>
@@ -3660,9 +3660,11 @@
         <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>19</v>
       </c>
@@ -3680,19 +3682,23 @@
         <v>19</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>19</v>
       </c>
@@ -3740,34 +3746,34 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>19</v>
@@ -3775,21 +3781,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>19</v>
@@ -3801,17 +3807,15 @@
         <v>19</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>19</v>
@@ -3848,31 +3852,31 @@
         <v>19</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>19</v>
@@ -3881,7 +3885,7 @@
         <v>19</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>19</v>
@@ -3895,46 +3899,44 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M16" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="N16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>19</v>
       </c>
@@ -3958,43 +3960,43 @@
         <v>19</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>188</v>
+        <v>19</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>19</v>
@@ -4003,7 +4005,7 @@
         <v>19</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>19</v>
@@ -4012,15 +4014,15 @@
         <v>19</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4037,25 +4039,25 @@
         <v>19</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>19</v>
@@ -4080,13 +4082,13 @@
         <v>19</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>198</v>
+        <v>113</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>19</v>
@@ -4104,7 +4106,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4125,7 +4127,7 @@
         <v>19</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>19</v>
@@ -4134,15 +4136,15 @@
         <v>19</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>202</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4165,19 +4167,19 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>19</v>
@@ -4187,10 +4189,10 @@
         <v>19</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>209</v>
+        <v>19</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>19</v>
@@ -4202,13 +4204,13 @@
         <v>19</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>19</v>
+        <v>205</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>19</v>
@@ -4226,7 +4228,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4247,7 +4249,7 @@
         <v>19</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>19</v>
@@ -4256,15 +4258,15 @@
         <v>19</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4272,7 +4274,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -4287,18 +4289,20 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="O19" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>19</v>
       </c>
@@ -4307,10 +4311,10 @@
         <v>19</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>19</v>
+        <v>215</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>19</v>
@@ -4346,7 +4350,7 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4355,7 +4359,7 @@
         <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>220</v>
+        <v>19</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>101</v>
@@ -4367,7 +4371,7 @@
         <v>19</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>19</v>
@@ -4376,15 +4380,15 @@
         <v>19</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4407,15 +4411,17 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>19</v>
@@ -4428,7 +4434,7 @@
         <v>19</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>19</v>
+        <v>226</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>19</v>
@@ -4473,7 +4479,7 @@
         <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>19</v>
+        <v>228</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>101</v>
@@ -4485,7 +4491,7 @@
         <v>19</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>19</v>
@@ -4494,15 +4500,15 @@
         <v>19</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4525,17 +4531,15 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>19</v>
@@ -4584,7 +4588,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4605,7 +4609,7 @@
         <v>19</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>19</v>
@@ -4614,19 +4618,17 @@
         <v>19</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>19</v>
       </c>
@@ -4647,20 +4649,18 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>161</v>
+        <v>241</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>162</v>
+        <v>242</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>163</v>
+        <v>243</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>19</v>
       </c>
@@ -4708,13 +4708,13 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>160</v>
+        <v>245</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>19</v>
@@ -4723,30 +4723,30 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>167</v>
+        <v>19</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>169</v>
+        <v>246</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>171</v>
+        <v>19</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>19</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>89</v>
@@ -4763,22 +4763,26 @@
         <v>19</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>173</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>19</v>
       </c>
@@ -4802,13 +4806,13 @@
         <v>19</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>19</v>
@@ -4826,28 +4830,28 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>175</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>19</v>
+        <v>255</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>19</v>
+        <v>256</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>177</v>
+        <v>257</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>19</v>
@@ -4861,21 +4865,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>178</v>
+        <v>258</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>19</v>
@@ -4884,21 +4888,21 @@
         <v>19</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>179</v>
+        <v>259</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>19</v>
       </c>
@@ -4922,43 +4926,41 @@
         <v>19</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>19</v>
+        <v>262</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>182</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>19</v>
@@ -4967,7 +4969,7 @@
         <v>19</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>19</v>
@@ -4981,10 +4983,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>183</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4995,32 +4997,28 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>109</v>
+        <v>264</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>184</v>
+        <v>265</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>19</v>
       </c>
@@ -5044,13 +5042,13 @@
         <v>19</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>188</v>
+        <v>19</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>19</v>
@@ -5068,13 +5066,13 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>190</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>19</v>
@@ -5089,7 +5087,7 @@
         <v>19</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>191</v>
+        <v>19</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>19</v>
@@ -5098,15 +5096,15 @@
         <v>19</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>192</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5126,23 +5124,19 @@
         <v>19</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>19</v>
       </c>
@@ -5166,13 +5160,13 @@
         <v>19</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>198</v>
+        <v>19</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>199</v>
+        <v>19</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>200</v>
+        <v>19</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>19</v>
@@ -5190,7 +5184,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5199,10 +5193,10 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>19</v>
@@ -5211,7 +5205,7 @@
         <v>19</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>19</v>
@@ -5220,26 +5214,26 @@
         <v>19</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>202</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>203</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>19</v>
@@ -5248,23 +5242,21 @@
         <v>19</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>19</v>
       </c>
@@ -5276,7 +5268,7 @@
         <v>19</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>209</v>
+        <v>19</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>19</v>
@@ -5312,19 +5304,19 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>19</v>
@@ -5333,7 +5325,7 @@
         <v>19</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>19</v>
@@ -5342,49 +5334,51 @@
         <v>19</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>212</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>213</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>19</v>
+        <v>270</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>215</v>
+        <v>271</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>216</v>
+        <v>272</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>19</v>
       </c>
@@ -5396,7 +5390,7 @@
         <v>19</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>218</v>
+        <v>19</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>19</v>
@@ -5432,19 +5426,19 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>219</v>
+        <v>273</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>220</v>
+        <v>19</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>19</v>
@@ -5453,7 +5447,7 @@
         <v>19</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>221</v>
+        <v>134</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>19</v>
@@ -5462,15 +5456,15 @@
         <v>19</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>222</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>223</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5478,7 +5472,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
@@ -5493,13 +5487,13 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5550,10 +5544,10 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>89</v>
@@ -5571,7 +5565,7 @@
         <v>19</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>19</v>
@@ -5580,15 +5574,15 @@
         <v>19</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>229</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>230</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5611,17 +5605,15 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>19</v>
@@ -5670,7 +5662,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>235</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5691,7 +5683,7 @@
         <v>19</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>236</v>
+        <v>19</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>19</v>
@@ -5700,15 +5692,15 @@
         <v>19</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>237</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5716,7 +5708,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>89</v>
@@ -5725,25 +5717,23 @@
         <v>19</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -5770,11 +5760,9 @@
       <c r="X31" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Y31" t="s" s="2">
-        <v>254</v>
-      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>19</v>
@@ -5792,10 +5780,10 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>89</v>
@@ -5807,13 +5795,13 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>256</v>
+        <v>19</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>258</v>
+        <v>19</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>19</v>
@@ -5822,15 +5810,15 @@
         <v>19</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>19</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5838,7 +5826,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>89</v>
@@ -5853,17 +5841,19 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>109</v>
+        <v>275</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>19</v>
@@ -5888,11 +5878,13 @@
         <v>19</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>263</v>
+        <v>19</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>19</v>
@@ -5910,10 +5902,10 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>89</v>
@@ -5928,27 +5920,27 @@
         <v>19</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>19</v>
+        <v>293</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>19</v>
+        <v>294</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>19</v>
+        <v>295</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>19</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5959,7 +5951,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>19</v>
@@ -5968,19 +5960,23 @@
         <v>19</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>19</v>
       </c>
@@ -6028,13 +6024,13 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>19</v>
@@ -6046,27 +6042,27 @@
         <v>19</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>19</v>
+        <v>293</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>19</v>
+        <v>294</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>19</v>
+        <v>295</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>19</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6077,7 +6073,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>19</v>
@@ -6086,19 +6082,21 @@
         <v>19</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>173</v>
+        <v>304</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>174</v>
+        <v>305</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>19</v>
       </c>
@@ -6146,56 +6144,56 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>175</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>19</v>
+        <v>293</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>19</v>
+        <v>294</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>19</v>
+        <v>295</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>19</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>19</v>
@@ -6204,21 +6202,21 @@
         <v>19</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>136</v>
+        <v>298</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>179</v>
+        <v>308</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>19</v>
       </c>
@@ -6266,80 +6264,80 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>182</v>
+        <v>307</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>19</v>
+        <v>311</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>19</v>
+        <v>293</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>19</v>
+        <v>294</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>19</v>
+        <v>295</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>19</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>271</v>
+        <v>19</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>272</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>273</v>
+        <v>314</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>157</v>
+        <v>315</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>158</v>
+        <v>316</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6388,19 +6386,19 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>274</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>19</v>
@@ -6409,24 +6407,24 @@
         <v>19</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>19</v>
+        <v>317</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>19</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6434,7 +6432,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>89</v>
@@ -6446,19 +6444,23 @@
         <v>19</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>276</v>
+        <v>199</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>277</v>
+        <v>320</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>19</v>
       </c>
@@ -6482,13 +6484,13 @@
         <v>19</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>19</v>
+        <v>324</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>19</v>
+        <v>325</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>19</v>
@@ -6506,10 +6508,10 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>89</v>
@@ -6530,7 +6532,7 @@
         <v>19</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>19</v>
+        <v>326</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>19</v>
@@ -6541,10 +6543,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>279</v>
+        <v>327</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>279</v>
+        <v>327</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6567,16 +6569,18 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>280</v>
+        <v>328</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>281</v>
+        <v>329</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>19</v>
       </c>
@@ -6624,7 +6628,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>279</v>
+        <v>327</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6639,13 +6643,13 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>19</v>
+        <v>331</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>19</v>
+        <v>333</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>19</v>
@@ -6654,15 +6658,15 @@
         <v>19</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>19</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6685,17 +6689,19 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>193</v>
+        <v>336</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>283</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>285</v>
+        <v>340</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>19</v>
@@ -6720,11 +6726,13 @@
         <v>19</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>286</v>
+        <v>19</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>19</v>
@@ -6742,7 +6750,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6760,7 +6768,7 @@
         <v>19</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>19</v>
@@ -6772,15 +6780,15 @@
         <v>19</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>289</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>289</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6791,7 +6799,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>19</v>
@@ -6800,22 +6808,22 @@
         <v>19</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>290</v>
+        <v>342</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>291</v>
+        <v>343</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>292</v>
+        <v>344</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>293</v>
+        <v>345</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>19</v>
@@ -6852,25 +6860,23 @@
         <v>19</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>289</v>
+        <v>341</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>19</v>
@@ -6882,27 +6888,27 @@
         <v>19</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>294</v>
+        <v>19</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>295</v>
+        <v>19</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>297</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>298</v>
+        <v>347</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>298</v>
+        <v>347</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6922,23 +6928,19 @@
         <v>19</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>299</v>
+        <v>222</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>300</v>
+        <v>176</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>19</v>
       </c>
@@ -6986,7 +6988,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>298</v>
+        <v>178</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6995,40 +6997,40 @@
         <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>294</v>
+        <v>19</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>295</v>
+        <v>19</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>297</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7044,21 +7046,21 @@
         <v>19</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>305</v>
+        <v>183</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>19</v>
       </c>
@@ -7106,7 +7108,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>304</v>
+        <v>186</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7118,66 +7120,68 @@
         <v>19</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>294</v>
+        <v>19</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>295</v>
+        <v>19</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>297</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>19</v>
+        <v>270</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>299</v>
+        <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -7226,45 +7230,45 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>308</v>
+        <v>273</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>312</v>
+        <v>19</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>294</v>
+        <v>19</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>295</v>
+        <v>19</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>297</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7272,7 +7276,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
@@ -7287,19 +7291,17 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>19</v>
@@ -7324,13 +7326,13 @@
         <v>19</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>19</v>
+        <v>354</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>19</v>
+        <v>355</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>19</v>
@@ -7348,10 +7350,10 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -7372,21 +7374,21 @@
         <v>19</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>318</v>
+        <v>19</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>319</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7394,7 +7396,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
@@ -7406,22 +7408,22 @@
         <v>19</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>323</v>
+        <v>359</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7446,13 +7448,13 @@
         <v>19</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>198</v>
+        <v>19</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>325</v>
+        <v>19</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>326</v>
+        <v>19</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>19</v>
@@ -7470,10 +7472,10 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>89</v>
@@ -7494,21 +7496,21 @@
         <v>19</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>19</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7531,17 +7533,17 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>329</v>
+        <v>365</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>19</v>
@@ -7590,7 +7592,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7605,32 +7607,34 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>333</v>
+        <v>19</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>334</v>
+        <v>19</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>335</v>
+        <v>368</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>336</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>19</v>
       </c>
@@ -7642,28 +7646,28 @@
         <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -7712,13 +7716,13 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>19</v>
@@ -7747,10 +7751,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7761,7 +7765,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>19</v>
@@ -7773,20 +7777,16 @@
         <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>265</v>
+        <v>222</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>342</v>
+        <v>176</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>19</v>
       </c>
@@ -7822,29 +7822,31 @@
         <v>19</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AC48" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD48" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>341</v>
+        <v>178</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>19</v>
@@ -7853,7 +7855,7 @@
         <v>19</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>19</v>
@@ -7867,21 +7869,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>19</v>
@@ -7893,15 +7895,17 @@
         <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7950,19 +7954,19 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>19</v>
@@ -7971,7 +7975,7 @@
         <v>19</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>19</v>
@@ -7985,14 +7989,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>154</v>
+        <v>270</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8005,24 +8009,26 @@
         <v>19</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>179</v>
+        <v>271</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>180</v>
+        <v>272</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
       </c>
@@ -8070,7 +8076,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>182</v>
+        <v>273</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8091,7 +8097,7 @@
         <v>19</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>19</v>
@@ -8105,45 +8111,43 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>271</v>
+        <v>19</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>136</v>
+        <v>199</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>272</v>
+        <v>351</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>158</v>
+        <v>353</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -8168,13 +8172,11 @@
         <v>19</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>19</v>
+        <v>375</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>19</v>
@@ -8192,19 +8194,19 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>274</v>
+        <v>350</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
@@ -8213,7 +8215,7 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>19</v>
@@ -8227,10 +8229,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8238,7 +8240,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
@@ -8250,21 +8252,19 @@
         <v>19</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>351</v>
+        <v>176</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>352</v>
+        <v>177</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>353</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>19</v>
       </c>
@@ -8288,13 +8288,13 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>198</v>
+        <v>19</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>355</v>
+        <v>19</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -8312,19 +8312,19 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>350</v>
+        <v>178</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>19</v>
@@ -8333,7 +8333,7 @@
         <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>19</v>
@@ -8347,21 +8347,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>19</v>
@@ -8370,23 +8370,21 @@
         <v>19</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>357</v>
+        <v>183</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>358</v>
+        <v>184</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>19</v>
       </c>
@@ -8422,31 +8420,31 @@
         <v>19</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>356</v>
+        <v>186</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>19</v>
@@ -8455,24 +8453,24 @@
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>363</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8483,7 +8481,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>19</v>
@@ -8495,17 +8493,19 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>214</v>
+        <v>382</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -8554,13 +8554,13 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>19</v>
@@ -8575,28 +8575,26 @@
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>19</v>
+        <v>388</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>368</v>
+        <v>389</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>19</v>
       </c>
@@ -8608,7 +8606,7 @@
         <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>19</v>
@@ -8617,20 +8615,16 @@
         <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>265</v>
+        <v>91</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>370</v>
+        <v>176</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>19</v>
       </c>
@@ -8678,19 +8672,19 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>341</v>
+        <v>178</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>19</v>
@@ -8699,7 +8693,7 @@
         <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>19</v>
@@ -8713,21 +8707,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>19</v>
@@ -8739,15 +8733,17 @@
         <v>19</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>19</v>
@@ -8784,31 +8780,31 @@
         <v>19</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>19</v>
@@ -8817,7 +8813,7 @@
         <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>19</v>
@@ -8831,21 +8827,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>348</v>
+        <v>395</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>19</v>
@@ -8854,21 +8850,23 @@
         <v>19</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>179</v>
+        <v>396</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>180</v>
+        <v>397</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>19</v>
       </c>
@@ -8877,7 +8875,7 @@
         <v>19</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>19</v>
+        <v>400</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>19</v>
@@ -8916,19 +8914,19 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>182</v>
+        <v>401</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>19</v>
@@ -8937,7 +8935,7 @@
         <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>19</v>
@@ -8946,51 +8944,49 @@
         <v>19</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>19</v>
+        <v>403</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>373</v>
+        <v>404</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>349</v>
+        <v>405</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>271</v>
+        <v>19</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>272</v>
+        <v>406</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>273</v>
+        <v>407</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>19</v>
       </c>
@@ -9038,19 +9034,19 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>274</v>
+        <v>409</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>19</v>
@@ -9059,7 +9055,7 @@
         <v>19</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>134</v>
+        <v>410</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>19</v>
@@ -9068,15 +9064,15 @@
         <v>19</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>19</v>
+        <v>411</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>374</v>
+        <v>412</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>350</v>
+        <v>413</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9084,7 +9080,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>89</v>
@@ -9099,17 +9095,17 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>193</v>
+        <v>109</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>352</v>
+        <v>415</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>353</v>
+        <v>416</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -9134,11 +9130,13 @@
         <v>19</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>375</v>
+        <v>19</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>19</v>
@@ -9156,16 +9154,16 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>350</v>
+        <v>417</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>19</v>
+        <v>418</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>101</v>
@@ -9177,7 +9175,7 @@
         <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>19</v>
+        <v>419</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>19</v>
@@ -9186,15 +9184,15 @@
         <v>19</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>19</v>
+        <v>420</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9214,19 +9212,21 @@
         <v>19</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>91</v>
+        <v>222</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>173</v>
+        <v>423</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>174</v>
+        <v>424</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
       </c>
@@ -9274,7 +9274,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>175</v>
+        <v>426</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9283,10 +9283,10 @@
         <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>176</v>
+        <v>418</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>19</v>
@@ -9295,7 +9295,7 @@
         <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>177</v>
+        <v>427</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>19</v>
@@ -9304,26 +9304,26 @@
         <v>19</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>19</v>
+        <v>428</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>378</v>
+        <v>429</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>379</v>
+        <v>430</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>19</v>
@@ -9332,21 +9332,23 @@
         <v>19</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>136</v>
+        <v>431</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>179</v>
+        <v>432</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>180</v>
+        <v>433</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>19</v>
       </c>
@@ -9382,31 +9384,31 @@
         <v>19</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>182</v>
+        <v>436</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>19</v>
@@ -9415,7 +9417,7 @@
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>177</v>
+        <v>437</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>19</v>
@@ -9424,15 +9426,15 @@
         <v>19</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>19</v>
+        <v>438</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>380</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>381</v>
+        <v>440</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9443,7 +9445,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>19</v>
@@ -9455,19 +9457,19 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>382</v>
+        <v>222</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>383</v>
+        <v>441</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>384</v>
+        <v>442</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>385</v>
+        <v>443</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>19</v>
@@ -9516,13 +9518,13 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>387</v>
+        <v>445</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>19</v>
@@ -9537,7 +9539,7 @@
         <v>19</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>388</v>
+        <v>446</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>19</v>
@@ -9546,15 +9548,15 @@
         <v>19</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>389</v>
+        <v>447</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>390</v>
+        <v>448</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>391</v>
+        <v>356</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9562,7 +9564,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>89</v>
@@ -9574,19 +9576,23 @@
         <v>19</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>173</v>
+        <v>357</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>19</v>
       </c>
@@ -9634,19 +9640,19 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>175</v>
+        <v>356</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>19</v>
@@ -9655,35 +9661,35 @@
         <v>19</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>19</v>
+        <v>363</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>392</v>
+        <v>449</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>19</v>
@@ -9692,21 +9698,21 @@
         <v>19</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>179</v>
+        <v>365</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>19</v>
       </c>
@@ -9742,31 +9748,31 @@
         <v>19</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>182</v>
+        <v>364</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>19</v>
@@ -9775,26 +9781,28 @@
         <v>19</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>19</v>
+        <v>368</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>394</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>19</v>
       </c>
@@ -9806,28 +9814,28 @@
         <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>103</v>
+        <v>264</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>396</v>
+        <v>451</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>397</v>
+        <v>343</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>398</v>
+        <v>344</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>399</v>
+        <v>345</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
@@ -9837,7 +9845,7 @@
         <v>19</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>400</v>
+        <v>19</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>19</v>
@@ -9876,13 +9884,13 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>401</v>
+        <v>341</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>19</v>
@@ -9897,7 +9905,7 @@
         <v>19</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>402</v>
+        <v>19</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>19</v>
@@ -9906,15 +9914,15 @@
         <v>19</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>403</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>404</v>
+        <v>452</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>405</v>
+        <v>347</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9934,20 +9942,18 @@
         <v>19</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>406</v>
+        <v>176</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>19</v>
@@ -9996,7 +10002,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>409</v>
+        <v>178</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10005,10 +10011,10 @@
         <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>19</v>
@@ -10017,7 +10023,7 @@
         <v>19</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>410</v>
+        <v>180</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>19</v>
@@ -10026,26 +10032,26 @@
         <v>19</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>411</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>412</v>
+        <v>453</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>413</v>
+        <v>348</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>19</v>
@@ -10054,21 +10060,21 @@
         <v>19</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>414</v>
+        <v>183</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>19</v>
       </c>
@@ -10116,19 +10122,19 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>417</v>
+        <v>186</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>418</v>
+        <v>19</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>19</v>
@@ -10137,7 +10143,7 @@
         <v>19</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>419</v>
+        <v>180</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>19</v>
@@ -10146,48 +10152,50 @@
         <v>19</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>420</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>422</v>
+        <v>349</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>19</v>
+        <v>270</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>423</v>
+        <v>271</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O68" t="s" s="2">
-        <v>425</v>
+        <v>158</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -10236,19 +10244,19 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>426</v>
+        <v>273</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>418</v>
+        <v>19</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>19</v>
@@ -10257,7 +10265,7 @@
         <v>19</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>427</v>
+        <v>134</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>19</v>
@@ -10266,15 +10274,15 @@
         <v>19</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>428</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>430</v>
+        <v>350</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10282,7 +10290,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>89</v>
@@ -10297,19 +10305,17 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>431</v>
+        <v>199</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>432</v>
+        <v>351</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>435</v>
+        <v>353</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>19</v>
@@ -10334,13 +10340,11 @@
         <v>19</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>19</v>
+        <v>456</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>19</v>
@@ -10358,10 +10362,10 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>436</v>
+        <v>350</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>89</v>
@@ -10379,7 +10383,7 @@
         <v>19</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>437</v>
+        <v>19</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>19</v>
@@ -10388,15 +10392,15 @@
         <v>19</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>438</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>440</v>
+        <v>377</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10416,23 +10420,19 @@
         <v>19</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>214</v>
+        <v>91</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>441</v>
+        <v>176</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>19</v>
       </c>
@@ -10480,7 +10480,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>445</v>
+        <v>178</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10489,10 +10489,10 @@
         <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>19</v>
@@ -10501,7 +10501,7 @@
         <v>19</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>446</v>
+        <v>180</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>19</v>
@@ -10510,26 +10510,26 @@
         <v>19</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>447</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>19</v>
@@ -10538,23 +10538,21 @@
         <v>19</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>357</v>
+        <v>183</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>358</v>
+        <v>184</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>19</v>
       </c>
@@ -10590,31 +10588,31 @@
         <v>19</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>356</v>
+        <v>186</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>19</v>
@@ -10623,24 +10621,24 @@
         <v>19</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>363</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10651,7 +10649,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>19</v>
@@ -10663,17 +10661,19 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>214</v>
+        <v>382</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -10722,13 +10722,13 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>19</v>
@@ -10743,28 +10743,26 @@
         <v>19</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>19</v>
+        <v>388</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>368</v>
+        <v>389</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>19</v>
       </c>
@@ -10776,7 +10774,7 @@
         <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>19</v>
@@ -10785,20 +10783,16 @@
         <v>19</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>265</v>
+        <v>91</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>451</v>
+        <v>176</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>19</v>
       </c>
@@ -10846,19 +10840,19 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>341</v>
+        <v>178</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>19</v>
@@ -10867,7 +10861,7 @@
         <v>19</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>19</v>
@@ -10881,21 +10875,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>19</v>
@@ -10907,15 +10901,17 @@
         <v>19</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>19</v>
@@ -10952,31 +10948,31 @@
         <v>19</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>19</v>
@@ -10985,7 +10981,7 @@
         <v>19</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>19</v>
@@ -10999,21 +10995,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>348</v>
+        <v>395</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>19</v>
@@ -11022,21 +11018,23 @@
         <v>19</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>179</v>
+        <v>396</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>180</v>
+        <v>397</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>19</v>
       </c>
@@ -11045,7 +11043,7 @@
         <v>19</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>19</v>
+        <v>463</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>19</v>
@@ -11084,19 +11082,19 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>182</v>
+        <v>401</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>19</v>
@@ -11105,7 +11103,7 @@
         <v>19</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>19</v>
@@ -11114,51 +11112,49 @@
         <v>19</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>19</v>
+        <v>403</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>349</v>
+        <v>405</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>271</v>
+        <v>19</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>272</v>
+        <v>406</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>273</v>
+        <v>407</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>19</v>
       </c>
@@ -11206,19 +11202,19 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>274</v>
+        <v>409</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>19</v>
@@ -11227,7 +11223,7 @@
         <v>19</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>134</v>
+        <v>410</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>19</v>
@@ -11236,15 +11232,15 @@
         <v>19</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>19</v>
+        <v>411</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>350</v>
+        <v>413</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11252,7 +11248,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>89</v>
@@ -11267,17 +11263,17 @@
         <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>193</v>
+        <v>109</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>352</v>
+        <v>415</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>353</v>
+        <v>416</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>19</v>
@@ -11302,11 +11298,13 @@
         <v>19</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>456</v>
+        <v>19</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>19</v>
@@ -11324,16 +11322,16 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>350</v>
+        <v>417</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>19</v>
+        <v>418</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>101</v>
@@ -11345,7 +11343,7 @@
         <v>19</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>19</v>
+        <v>419</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>19</v>
@@ -11354,15 +11352,15 @@
         <v>19</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>19</v>
+        <v>420</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11382,19 +11380,21 @@
         <v>19</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>91</v>
+        <v>222</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>173</v>
+        <v>423</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>174</v>
+        <v>424</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>19</v>
       </c>
@@ -11442,7 +11442,7 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>175</v>
+        <v>426</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11451,10 +11451,10 @@
         <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>176</v>
+        <v>418</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>19</v>
@@ -11463,7 +11463,7 @@
         <v>19</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>177</v>
+        <v>427</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>19</v>
@@ -11472,26 +11472,26 @@
         <v>19</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>19</v>
+        <v>428</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>379</v>
+        <v>430</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>19</v>
@@ -11500,21 +11500,23 @@
         <v>19</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>136</v>
+        <v>431</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>179</v>
+        <v>432</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>180</v>
+        <v>433</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>19</v>
       </c>
@@ -11550,31 +11552,31 @@
         <v>19</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>182</v>
+        <v>436</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>19</v>
@@ -11583,7 +11585,7 @@
         <v>19</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>177</v>
+        <v>437</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>19</v>
@@ -11592,15 +11594,15 @@
         <v>19</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>19</v>
+        <v>438</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>381</v>
+        <v>440</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11611,7 +11613,7 @@
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>19</v>
@@ -11623,19 +11625,19 @@
         <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>382</v>
+        <v>222</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>383</v>
+        <v>441</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>384</v>
+        <v>442</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>385</v>
+        <v>443</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>19</v>
@@ -11684,13 +11686,13 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>387</v>
+        <v>445</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>19</v>
@@ -11705,7 +11707,7 @@
         <v>19</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>388</v>
+        <v>446</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>19</v>
@@ -11714,15 +11716,15 @@
         <v>19</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>389</v>
+        <v>447</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>391</v>
+        <v>356</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11730,7 +11732,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>89</v>
@@ -11742,19 +11744,23 @@
         <v>19</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>173</v>
+        <v>357</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>19</v>
       </c>
@@ -11802,19 +11808,19 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>175</v>
+        <v>356</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>19</v>
@@ -11823,35 +11829,35 @@
         <v>19</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>19</v>
+        <v>363</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>19</v>
@@ -11860,21 +11866,21 @@
         <v>19</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>179</v>
+        <v>365</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>19</v>
       </c>
@@ -11910,31 +11916,31 @@
         <v>19</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>182</v>
+        <v>364</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>19</v>
@@ -11943,24 +11949,24 @@
         <v>19</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>19</v>
+        <v>368</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>395</v>
+        <v>471</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11983,19 +11989,17 @@
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>103</v>
+        <v>472</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>396</v>
+        <v>473</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>19</v>
@@ -12005,7 +12009,7 @@
         <v>19</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>463</v>
+        <v>19</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>19</v>
@@ -12044,7 +12048,7 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>401</v>
+        <v>471</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12065,7 +12069,7 @@
         <v>19</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>402</v>
+        <v>19</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>19</v>
@@ -12074,15 +12078,15 @@
         <v>19</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>403</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>405</v>
+        <v>476</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12105,18 +12109,18 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>406</v>
+        <v>477</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>19</v>
       </c>
@@ -12164,7 +12168,7 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>409</v>
+        <v>476</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12185,35 +12189,35 @@
         <v>19</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>410</v>
+        <v>19</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>19</v>
+        <v>480</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>411</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>413</v>
+        <v>481</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>19</v>
+        <v>482</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>19</v>
@@ -12222,20 +12226,22 @@
         <v>19</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>109</v>
+        <v>264</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>414</v>
+        <v>483</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="O85" t="s" s="2">
-        <v>416</v>
+        <v>486</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>19</v>
@@ -12284,16 +12290,16 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>417</v>
+        <v>481</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>418</v>
+        <v>19</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>101</v>
@@ -12305,7 +12311,7 @@
         <v>19</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>419</v>
+        <v>19</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>19</v>
@@ -12314,15 +12320,15 @@
         <v>19</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>420</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>422</v>
+        <v>487</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12342,21 +12348,19 @@
         <v>19</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>423</v>
+        <v>176</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>424</v>
+        <v>177</v>
       </c>
       <c r="N86" s="2"/>
-      <c r="O86" t="s" s="2">
-        <v>425</v>
-      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>19</v>
       </c>
@@ -12404,7 +12408,7 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>426</v>
+        <v>178</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12413,10 +12417,10 @@
         <v>89</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>418</v>
+        <v>179</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>19</v>
@@ -12425,7 +12429,7 @@
         <v>19</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>427</v>
+        <v>180</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>19</v>
@@ -12434,26 +12438,26 @@
         <v>19</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>428</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>430</v>
+        <v>488</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>19</v>
@@ -12462,23 +12466,21 @@
         <v>19</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>431</v>
+        <v>136</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>432</v>
+        <v>183</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>433</v>
+        <v>184</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>19</v>
       </c>
@@ -12526,19 +12528,19 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>436</v>
+        <v>186</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>19</v>
@@ -12547,7 +12549,7 @@
         <v>19</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>437</v>
+        <v>180</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>19</v>
@@ -12556,50 +12558,50 @@
         <v>19</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>438</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>440</v>
+        <v>489</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>19</v>
+        <v>270</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>441</v>
+        <v>271</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>442</v>
+        <v>272</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>443</v>
+        <v>157</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>444</v>
+        <v>158</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>19</v>
@@ -12648,19 +12650,19 @@
         <v>19</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>445</v>
+        <v>273</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>19</v>
@@ -12669,7 +12671,7 @@
         <v>19</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>446</v>
+        <v>134</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>19</v>
@@ -12678,15 +12680,15 @@
         <v>19</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>447</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>356</v>
+        <v>490</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12694,7 +12696,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>89</v>
@@ -12709,19 +12711,19 @@
         <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>357</v>
+        <v>491</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>358</v>
+        <v>492</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>359</v>
+        <v>493</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>360</v>
+        <v>494</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>19</v>
@@ -12746,13 +12748,13 @@
         <v>19</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>19</v>
+        <v>495</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>19</v>
+        <v>496</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>19</v>
@@ -12770,10 +12772,10 @@
         <v>19</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>356</v>
+        <v>490</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>89</v>
@@ -12794,21 +12796,21 @@
         <v>19</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>363</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>364</v>
+        <v>497</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12828,20 +12830,22 @@
         <v>19</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>365</v>
+        <v>498</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="O90" t="s" s="2">
-        <v>367</v>
+        <v>501</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>19</v>
@@ -12866,13 +12870,11 @@
         <v>19</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>19</v>
+        <v>503</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>19</v>
@@ -12890,7 +12892,7 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>364</v>
+        <v>497</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12914,21 +12916,21 @@
         <v>19</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>368</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>471</v>
+        <v>504</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>471</v>
+        <v>504</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12948,20 +12950,20 @@
         <v>19</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>472</v>
+        <v>199</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>19</v>
@@ -12986,13 +12988,11 @@
         <v>19</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>19</v>
+        <v>508</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>19</v>
@@ -13010,7 +13010,7 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>471</v>
+        <v>504</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13045,10 +13045,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13068,20 +13068,20 @@
         <v>19</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>477</v>
+        <v>510</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>478</v>
+        <v>511</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>19</v>
@@ -13106,13 +13106,11 @@
         <v>19</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>19</v>
+        <v>513</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>19</v>
@@ -13130,7 +13128,7 @@
         <v>19</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13154,7 +13152,7 @@
         <v>19</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>480</v>
+        <v>19</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>19</v>
@@ -13165,21 +13163,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>481</v>
+        <v>514</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>481</v>
+        <v>514</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>482</v>
+        <v>19</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>19</v>
@@ -13191,19 +13189,17 @@
         <v>19</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>265</v>
+        <v>199</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>486</v>
+        <v>512</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>19</v>
@@ -13228,13 +13224,11 @@
         <v>19</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>19</v>
+        <v>517</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>19</v>
@@ -13252,13 +13246,13 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>481</v>
+        <v>514</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>19</v>
@@ -13287,10 +13281,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>487</v>
+        <v>518</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>487</v>
+        <v>518</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13310,19 +13304,23 @@
         <v>19</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>214</v>
+        <v>519</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>173</v>
+        <v>520</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>19</v>
       </c>
@@ -13370,7 +13368,7 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>175</v>
+        <v>518</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13379,10 +13377,10 @@
         <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>19</v>
@@ -13391,28 +13389,28 @@
         <v>19</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>19</v>
+        <v>368</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>488</v>
+        <v>524</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>488</v>
+        <v>524</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13431,18 +13429,18 @@
         <v>19</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>136</v>
+        <v>264</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>179</v>
+        <v>525</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>19</v>
       </c>
@@ -13490,7 +13488,7 @@
         <v>19</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>182</v>
+        <v>524</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13502,7 +13500,7 @@
         <v>19</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>19</v>
@@ -13511,7 +13509,7 @@
         <v>19</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>19</v>
@@ -13525,46 +13523,42 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>489</v>
+        <v>527</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>489</v>
+        <v>527</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>271</v>
+        <v>19</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>272</v>
+        <v>176</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>19</v>
       </c>
@@ -13612,19 +13606,19 @@
         <v>19</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>274</v>
+        <v>178</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>19</v>
@@ -13633,7 +13627,7 @@
         <v>19</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>19</v>
@@ -13647,21 +13641,21 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>490</v>
+        <v>528</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>490</v>
+        <v>528</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>19</v>
@@ -13670,23 +13664,21 @@
         <v>19</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>491</v>
+        <v>183</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>492</v>
+        <v>184</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>19</v>
       </c>
@@ -13710,13 +13702,13 @@
         <v>19</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>198</v>
+        <v>19</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>495</v>
+        <v>19</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>496</v>
+        <v>19</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>19</v>
@@ -13734,19 +13726,19 @@
         <v>19</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>490</v>
+        <v>186</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>19</v>
@@ -13755,7 +13747,7 @@
         <v>19</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>19</v>
@@ -13769,45 +13761,45 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>19</v>
+        <v>270</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>498</v>
+        <v>271</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>499</v>
+        <v>272</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>500</v>
+        <v>157</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>501</v>
+        <v>158</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>19</v>
@@ -13832,11 +13824,13 @@
         <v>19</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>503</v>
+        <v>19</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>19</v>
@@ -13854,19 +13848,19 @@
         <v>19</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>497</v>
+        <v>273</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>19</v>
@@ -13875,7 +13869,7 @@
         <v>19</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>19</v>
@@ -13889,10 +13883,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13900,7 +13894,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>89</v>
@@ -13912,20 +13906,20 @@
         <v>19</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>19</v>
@@ -13952,9 +13946,11 @@
       <c r="X99" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="Y99" s="2"/>
+      <c r="Y99" t="s" s="2">
+        <v>534</v>
+      </c>
       <c r="Z99" t="s" s="2">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>19</v>
@@ -13972,10 +13968,10 @@
         <v>19</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>89</v>
@@ -14007,10 +14003,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>509</v>
+        <v>536</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>509</v>
+        <v>536</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14030,20 +14026,20 @@
         <v>19</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>510</v>
+        <v>537</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>511</v>
+        <v>538</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>19</v>
@@ -14068,11 +14064,13 @@
         <v>19</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="Y100" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z100" t="s" s="2">
-        <v>513</v>
+        <v>19</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>19</v>
@@ -14090,7 +14088,7 @@
         <v>19</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>509</v>
+        <v>536</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14125,10 +14123,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14151,17 +14149,19 @@
         <v>19</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>193</v>
+        <v>431</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>542</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>543</v>
+      </c>
       <c r="O101" t="s" s="2">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>19</v>
@@ -14186,11 +14186,13 @@
         <v>19</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="Y101" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z101" t="s" s="2">
-        <v>517</v>
+        <v>19</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>19</v>
@@ -14208,7 +14210,7 @@
         <v>19</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14243,10 +14245,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>518</v>
+        <v>545</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>518</v>
+        <v>545</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14257,7 +14259,7 @@
         <v>78</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>19</v>
@@ -14266,22 +14268,20 @@
         <v>19</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>519</v>
+        <v>546</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>520</v>
+        <v>547</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>523</v>
+        <v>549</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>19</v>
@@ -14330,13 +14330,13 @@
         <v>19</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>518</v>
+        <v>545</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>19</v>
@@ -14351,24 +14351,24 @@
         <v>19</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>361</v>
+        <v>294</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>362</v>
+        <v>295</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>368</v>
+        <v>550</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>524</v>
+        <v>551</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>524</v>
+        <v>551</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14379,7 +14379,7 @@
         <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>19</v>
@@ -14391,17 +14391,17 @@
         <v>19</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>265</v>
+        <v>552</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>525</v>
+        <v>553</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>526</v>
+        <v>554</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>486</v>
+        <v>555</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>19</v>
@@ -14450,13 +14450,13 @@
         <v>19</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>524</v>
+        <v>551</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>19</v>
@@ -14483,970 +14483,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="P107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="P108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="P110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="P111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AP111">
+  <autoFilter ref="A1:AP103">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15456,7 +14494,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI110">
+  <conditionalFormatting sqref="A2:AI102">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T20:06:39+00:00</t>
+    <t>2024-11-14T06:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T06:51:52+00:00</t>
+    <t>2024-11-14T14:31:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:31:22+00:00</t>
+    <t>2024-11-14T14:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:34:15+00:00</t>
+    <t>2024-11-14T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:43:46+00:00</t>
+    <t>2024-11-15T18:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T18:55:56+00:00</t>
+    <t>2024-11-15T19:04:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:04:50+00:00</t>
+    <t>2024-11-15T19:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:21:45+00:00</t>
+    <t>2024-11-15T20:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:14:47+00:00</t>
+    <t>2024-11-17T19:44:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:44:33+00:00</t>
+    <t>2024-11-19T10:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T10:30:26+00:00</t>
+    <t>2025-02-10T09:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
